--- a/artfynd/S 1737-2022 artfynd.xlsx
+++ b/artfynd/S 1737-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675794</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675865</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675750</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675854</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675815</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88676009</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675698</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675724</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1628,6 +1673,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675734</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1729,6 +1779,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675763</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1830,6 +1885,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675837</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675615</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675684</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2155,6 +2225,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675755</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2247,8 +2322,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88675994</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1737-2022 artfynd.xlsx
+++ b/artfynd/S 1737-2022 artfynd.xlsx
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88675750</v>
+        <v>88675994</v>
       </c>
       <c r="B4" t="n">
-        <v>91893</v>
+        <v>89206</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4660</v>
+        <v>4393</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Papegojvaxing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Herink</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603464</v>
+        <v>603499</v>
       </c>
       <c r="R4" t="n">
-        <v>6556845</v>
+        <v>6556947</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,11 +987,6 @@
           <t>2020-09-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På död asp.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1016,13 +1011,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88675750</t>
+          <t>https://artportalen.se/Sighting/88675994</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88675854</v>
+        <v>88675750</v>
       </c>
       <c r="B5" t="n">
         <v>91893</v>
@@ -1060,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603448</v>
+        <v>603464</v>
       </c>
       <c r="R5" t="n">
-        <v>6556879</v>
+        <v>6556845</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1095,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På låga och högstubbe av asp.</t>
+          <t>På död asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,16 +1122,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88675854</t>
+          <t>https://artportalen.se/Sighting/88675750</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88675815</v>
+        <v>88675854</v>
       </c>
       <c r="B6" t="n">
-        <v>91966</v>
+        <v>91893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5321</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603479</v>
+        <v>603448</v>
       </c>
       <c r="R6" t="n">
-        <v>6556846</v>
+        <v>6556879</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1211,7 +1206,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På grov kapad asplåga.</t>
+          <t>På låga och högstubbe av asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,13 +1233,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88675815</t>
+          <t>https://artportalen.se/Sighting/88675854</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88676009</v>
+        <v>88675815</v>
       </c>
       <c r="B7" t="n">
         <v>91966</v>
@@ -1282,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603456</v>
+        <v>603479</v>
       </c>
       <c r="R7" t="n">
-        <v>6556953</v>
+        <v>6556846</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1322,7 +1317,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På asplåga.</t>
+          <t>På grov kapad asplåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,16 +1344,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88676009</t>
+          <t>https://artportalen.se/Sighting/88675815</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88675698</v>
+        <v>88676009</v>
       </c>
       <c r="B8" t="n">
-        <v>92348</v>
+        <v>91966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,33 +1361,25 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>5321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1401,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603389</v>
+        <v>603456</v>
       </c>
       <c r="R8" t="n">
-        <v>6556946</v>
+        <v>6556953</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,6 +1426,11 @@
           <t>2020-09-21</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asplåga.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1463,42 +1455,50 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88675698</t>
+          <t>https://artportalen.se/Sighting/88676009</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88675724</v>
+        <v>88675698</v>
       </c>
       <c r="B9" t="n">
-        <v>91930</v>
+        <v>92348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603418</v>
+        <v>603389</v>
       </c>
       <c r="R9" t="n">
-        <v>6556852</v>
+        <v>6556946</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,13 +1569,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88675724</t>
+          <t>https://artportalen.se/Sighting/88675698</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88675734</v>
+        <v>88675724</v>
       </c>
       <c r="B10" t="n">
         <v>91930</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603416</v>
+        <v>603418</v>
       </c>
       <c r="R10" t="n">
-        <v>6556844</v>
+        <v>6556852</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1675,13 +1675,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88675734</t>
+          <t>https://artportalen.se/Sighting/88675724</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>88675763</v>
+        <v>88675734</v>
       </c>
       <c r="B11" t="n">
         <v>91930</v>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603458</v>
+        <v>603416</v>
       </c>
       <c r="R11" t="n">
-        <v>6556836</v>
+        <v>6556844</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1781,13 +1781,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88675763</t>
+          <t>https://artportalen.se/Sighting/88675734</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>88675837</v>
+        <v>88675763</v>
       </c>
       <c r="B12" t="n">
         <v>91930</v>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603464</v>
+        <v>603458</v>
       </c>
       <c r="R12" t="n">
-        <v>6556866</v>
+        <v>6556836</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1887,53 +1887,43 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88675837</t>
+          <t>https://artportalen.se/Sighting/88675763</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>88675615</v>
+        <v>88675837</v>
       </c>
       <c r="B13" t="n">
-        <v>44177</v>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101735</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1941,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603414</v>
+        <v>603464</v>
       </c>
       <c r="R13" t="n">
-        <v>6557068</v>
+        <v>6556866</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1979,11 +1969,6 @@
           <t>2020-09-21</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Levande larv i fnöskticka på låga av björk.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2008,16 +1993,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88675615</t>
+          <t>https://artportalen.se/Sighting/88675837</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>88675684</v>
+        <v>88675615</v>
       </c>
       <c r="B14" t="n">
-        <v>4781</v>
+        <v>44177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,30 +2010,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>101735</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2058,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603367</v>
+        <v>603414</v>
       </c>
       <c r="R14" t="n">
-        <v>6556993</v>
+        <v>6557068</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2096,6 +2085,11 @@
           <t>2020-09-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Levande larv i fnöskticka på låga av björk.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2120,16 +2114,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88675684</t>
+          <t>https://artportalen.se/Sighting/88675615</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>88675755</v>
+        <v>88675684</v>
       </c>
       <c r="B15" t="n">
-        <v>101326</v>
+        <v>4781</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,27 +2131,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2165,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603464</v>
+        <v>603367</v>
       </c>
       <c r="R15" t="n">
-        <v>6556845</v>
+        <v>6556993</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2227,16 +2226,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88675755</t>
+          <t>https://artportalen.se/Sighting/88675684</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>88675994</v>
+        <v>88675755</v>
       </c>
       <c r="B16" t="n">
-        <v>89060</v>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,17 +2243,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>239221</v>
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus var. psittacinus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2262,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603499</v>
+        <v>603464</v>
       </c>
       <c r="R16" t="n">
-        <v>6556947</v>
+        <v>6556845</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2324,7 +2333,7 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88675994</t>
+          <t>https://artportalen.se/Sighting/88675755</t>
         </is>
       </c>
     </row>

--- a/artfynd/S 1737-2022 artfynd.xlsx
+++ b/artfynd/S 1737-2022 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>88675994</v>
       </c>
       <c r="B4" t="n">
-        <v>89206</v>
+        <v>89207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1737-2022 artfynd.xlsx
+++ b/artfynd/S 1737-2022 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>88675994</v>
       </c>
       <c r="B4" t="n">
-        <v>89207</v>
+        <v>89213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1737-2022 artfynd.xlsx
+++ b/artfynd/S 1737-2022 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>88675994</v>
       </c>
       <c r="B4" t="n">
-        <v>89213</v>
+        <v>89220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1737-2022 artfynd.xlsx
+++ b/artfynd/S 1737-2022 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>88675994</v>
       </c>
       <c r="B4" t="n">
-        <v>89220</v>
+        <v>89221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1737-2022 artfynd.xlsx
+++ b/artfynd/S 1737-2022 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>88675994</v>
       </c>
       <c r="B4" t="n">
-        <v>89221</v>
+        <v>89234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1737-2022 artfynd.xlsx
+++ b/artfynd/S 1737-2022 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>88675994</v>
       </c>
       <c r="B4" t="n">
-        <v>89234</v>
+        <v>89235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
